--- a/pca-interpretable-clustering/classified_data/Element.xlsx
+++ b/pca-interpretable-clustering/classified_data/Element.xlsx
@@ -1800,7 +1800,7 @@
         <v>73.92662</v>
       </c>
       <c r="H2">
-        <v>429.5667</v>
+        <v>429.566703</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1826,7 +1826,7 @@
         <v>1.28768</v>
       </c>
       <c r="H3">
-        <v>59.37398</v>
+        <v>59.37398225</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1852,7 +1852,7 @@
         <v>2.59708</v>
       </c>
       <c r="H4">
-        <v>101.95254</v>
+        <v>101.9525378</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1878,7 +1878,7 @@
         <v>31.82629</v>
       </c>
       <c r="H5">
-        <v>110.36623</v>
+        <v>110.3662295</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1904,7 +1904,7 @@
         <v>54.03488</v>
       </c>
       <c r="H6">
-        <v>187.02852</v>
+        <v>134.0812971</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1930,7 +1930,7 @@
         <v>1.03719</v>
       </c>
       <c r="H7">
-        <v>51.84458</v>
+        <v>51.84457882</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1956,7 +1956,7 @@
         <v>1.44527</v>
       </c>
       <c r="H8">
-        <v>40.26071</v>
+        <v>40.26071166</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1982,7 +1982,7 @@
         <v>30.7179</v>
       </c>
       <c r="H9">
-        <v>138.83259</v>
+        <v>138.8325913</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2008,7 +2008,7 @@
         <v>274.71472</v>
       </c>
       <c r="H10">
-        <v>285.87821</v>
+        <v>285.8782088</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2034,7 +2034,7 @@
         <v>271.26964</v>
       </c>
       <c r="H11">
-        <v>290.15531</v>
+        <v>274.8816811</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2060,7 +2060,7 @@
         <v>78.44301</v>
       </c>
       <c r="H12">
-        <v>211.8237</v>
+        <v>211.8237022</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2086,7 +2086,7 @@
         <v>7.03485</v>
       </c>
       <c r="H13">
-        <v>89.89944</v>
+        <v>89.89944414</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2112,7 +2112,7 @@
         <v>7.81439</v>
       </c>
       <c r="H14">
-        <v>78.14393</v>
+        <v>78.14392709000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2138,7 +2138,7 @@
         <v>75.02500000000001</v>
       </c>
       <c r="H15">
-        <v>278.05498</v>
+        <v>278.0549819</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2164,7 +2164,7 @@
         <v>3.15005</v>
       </c>
       <c r="H16">
-        <v>87.68277999999999</v>
+        <v>87.68278445999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2190,7 +2190,7 @@
         <v>3.89862</v>
       </c>
       <c r="H17">
-        <v>117.54126</v>
+        <v>117.5412623</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2216,7 +2216,7 @@
         <v>48.49526</v>
       </c>
       <c r="H18">
-        <v>211.35939</v>
+        <v>211.3593911</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2242,7 +2242,7 @@
         <v>8.325749999999999</v>
       </c>
       <c r="H19">
-        <v>59.00213</v>
+        <v>59.00212705</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2268,7 +2268,7 @@
         <v>31.44685</v>
       </c>
       <c r="H20">
-        <v>272.55242</v>
+        <v>352.956993</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2294,7 +2294,7 @@
         <v>525.52797</v>
       </c>
       <c r="H21">
-        <v>1482.9243</v>
+        <v>1397.983439</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2320,7 +2320,7 @@
         <v>219.18035</v>
       </c>
       <c r="H22">
-        <v>1043.18071</v>
+        <v>1043.180706</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2346,7 +2346,7 @@
         <v>76.32581999999999</v>
       </c>
       <c r="H23">
-        <v>244.47585</v>
+        <v>244.4758529</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2372,7 +2372,7 @@
         <v>101.23455</v>
       </c>
       <c r="H24">
-        <v>325.70718</v>
+        <v>325.7071845</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2398,7 +2398,7 @@
         <v>163.97248</v>
       </c>
       <c r="H25">
-        <v>244.65734</v>
+        <v>244.6573427</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2424,7 +2424,7 @@
         <v>936.09083</v>
       </c>
       <c r="H26">
-        <v>2019.27412</v>
+        <v>2019.274118</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2450,7 +2450,7 @@
         <v>169.71312</v>
       </c>
       <c r="H27">
-        <v>889.94181</v>
+        <v>889.9418106000001</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2476,7 +2476,7 @@
         <v>117.90031</v>
       </c>
       <c r="H28">
-        <v>553.22789</v>
+        <v>553.227891</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2502,7 +2502,7 @@
         <v>98.53421</v>
       </c>
       <c r="H29">
-        <v>308.35364</v>
+        <v>308.3536397</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2528,7 +2528,7 @@
         <v>157.86896</v>
       </c>
       <c r="H30">
-        <v>605.59969</v>
+        <v>605.5996879</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2554,7 +2554,7 @@
         <v>64.00830999999999</v>
       </c>
       <c r="H31">
-        <v>206.7208</v>
+        <v>113.006906</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2580,7 +2580,7 @@
         <v>97.46716000000001</v>
       </c>
       <c r="H32">
-        <v>317.44276</v>
+        <v>317.442762</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2606,7 +2606,7 @@
         <v>2.70685</v>
       </c>
       <c r="H33">
-        <v>84.18644</v>
+        <v>84.18644485999999</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2632,7 +2632,7 @@
         <v>9.13425</v>
       </c>
       <c r="H34">
-        <v>102.50226</v>
+        <v>170.9112683</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2658,7 +2658,7 @@
         <v>145.21832</v>
       </c>
       <c r="H35">
-        <v>608.0539199999999</v>
+        <v>608.0539241</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2684,7 +2684,7 @@
         <v>35.67547</v>
       </c>
       <c r="H36">
-        <v>157.81865</v>
+        <v>157.8186535</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2710,7 +2710,7 @@
         <v>9.93488</v>
       </c>
       <c r="H37">
-        <v>162.73543</v>
+        <v>162.7354305</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2736,7 +2736,7 @@
         <v>35.70238</v>
       </c>
       <c r="H38">
-        <v>158.01972</v>
+        <v>158.0197191</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2762,7 +2762,7 @@
         <v>14.76815</v>
       </c>
       <c r="H39">
-        <v>127.86951</v>
+        <v>127.8695147</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2788,7 +2788,7 @@
         <v>406.15555</v>
       </c>
       <c r="H40">
-        <v>1413.69109</v>
+        <v>1413.691095</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2814,7 +2814,7 @@
         <v>11.31563</v>
       </c>
       <c r="H41">
-        <v>332.31998</v>
+        <v>332.3199763</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2840,7 +2840,7 @@
         <v>71.08235999999999</v>
       </c>
       <c r="H42">
-        <v>182.30271</v>
+        <v>182.3027078</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2866,7 +2866,7 @@
         <v>22.80299</v>
       </c>
       <c r="H43">
-        <v>94.96569</v>
+        <v>94.96569208</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2892,7 +2892,7 @@
         <v>50.31759</v>
       </c>
       <c r="H44">
-        <v>186.10393</v>
+        <v>153.5873366</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2918,7 +2918,7 @@
         <v>50.1004</v>
       </c>
       <c r="H45">
-        <v>224.23952</v>
+        <v>229.6358912</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2944,7 +2944,7 @@
         <v>195.24479</v>
       </c>
       <c r="H46">
-        <v>977.75293</v>
+        <v>977.7529251</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2970,7 +2970,7 @@
         <v>1119.01149</v>
       </c>
       <c r="H47">
-        <v>2219.51836</v>
+        <v>2219.518356</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2996,7 +2996,7 @@
         <v>67.12426000000001</v>
       </c>
       <c r="H48">
-        <v>186.59116</v>
+        <v>166.2203115</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3022,7 +3022,7 @@
         <v>34.98893</v>
       </c>
       <c r="H49">
-        <v>182.22335</v>
+        <v>182.2233538</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -3048,7 +3048,7 @@
         <v>7.03474</v>
       </c>
       <c r="H50">
-        <v>51.66438</v>
+        <v>75.09886503</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3074,7 +3074,7 @@
         <v>9.848240000000001</v>
       </c>
       <c r="H51">
-        <v>63.3367</v>
+        <v>63.33669687</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3100,7 +3100,7 @@
         <v>68.42489999999999</v>
       </c>
       <c r="H52">
-        <v>186.34606</v>
+        <v>169.8591128</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -3126,7 +3126,7 @@
         <v>94.17703</v>
       </c>
       <c r="H53">
-        <v>458.85715</v>
+        <v>464.809126</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3152,7 +3152,7 @@
         <v>2.66461</v>
       </c>
       <c r="H54">
-        <v>59.41431</v>
+        <v>27.27094093</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -3178,7 +3178,7 @@
         <v>469.76037</v>
       </c>
       <c r="H55">
-        <v>400.98036</v>
+        <v>381.9696095</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -3204,7 +3204,7 @@
         <v>57.77083</v>
       </c>
       <c r="H56">
-        <v>181.80322</v>
+        <v>153.790709</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -3256,7 +3256,7 @@
         <v>70.34265000000001</v>
       </c>
       <c r="H58">
-        <v>185.50083</v>
+        <v>185.5008344</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3282,7 +3282,7 @@
         <v>23.98775</v>
       </c>
       <c r="H59">
-        <v>112.78082</v>
+        <v>112.7808245</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -3308,7 +3308,7 @@
         <v>157.72883</v>
       </c>
       <c r="H60">
-        <v>470.54901</v>
+        <v>445.0041903</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -3334,7 +3334,7 @@
         <v>21.1444</v>
       </c>
       <c r="H61">
-        <v>1073.85665</v>
+        <v>1073.856649</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3360,7 +3360,7 @@
         <v>4.704</v>
       </c>
       <c r="H62">
-        <v>42.25117</v>
+        <v>42.25116585</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3386,7 +3386,7 @@
         <v>13.80779</v>
       </c>
       <c r="H63">
-        <v>369.98654</v>
+        <v>369.9865436</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -3412,7 +3412,7 @@
         <v>144.59645</v>
       </c>
       <c r="H64">
-        <v>574.7798</v>
+        <v>574.7797974</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -3438,7 +3438,7 @@
         <v>41.91591</v>
       </c>
       <c r="H65">
-        <v>132.91355</v>
+        <v>132.9135493</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3464,7 +3464,7 @@
         <v>65.29577999999999</v>
       </c>
       <c r="H66">
-        <v>184.27527</v>
+        <v>126.8973141</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -3490,7 +3490,7 @@
         <v>69.89843999999999</v>
       </c>
       <c r="H67">
-        <v>188.74677</v>
+        <v>131.5200317</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3516,7 +3516,7 @@
         <v>41.66196</v>
       </c>
       <c r="H68">
-        <v>163.10005</v>
+        <v>120.8416213</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -3542,7 +3542,7 @@
         <v>53.08049</v>
       </c>
       <c r="H69">
-        <v>179.01239</v>
+        <v>174.8434343</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -3568,7 +3568,7 @@
         <v>56.39495</v>
       </c>
       <c r="H70">
-        <v>183.52344</v>
+        <v>178.7842197</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -3594,7 +3594,7 @@
         <v>498.80717</v>
       </c>
       <c r="H71">
-        <v>414.72309</v>
+        <v>368.2906006</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -3620,7 +3620,7 @@
         <v>59.15201</v>
       </c>
       <c r="H72">
-        <v>184.0842</v>
+        <v>181.0425827</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3646,7 +3646,7 @@
         <v>59.42286</v>
       </c>
       <c r="H73">
-        <v>177.51323</v>
+        <v>166.9818826</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3672,7 +3672,7 @@
         <v>76.4208</v>
       </c>
       <c r="H74">
-        <v>194.40281</v>
+        <v>173.0429639</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -3698,7 +3698,7 @@
         <v>85.86481000000001</v>
       </c>
       <c r="H75">
-        <v>229.10257</v>
+        <v>227.1193477</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -3724,7 +3724,7 @@
         <v>292.64419</v>
       </c>
       <c r="H76">
-        <v>1373.82619</v>
+        <v>1373.826187</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -3750,7 +3750,7 @@
         <v>36.34923</v>
       </c>
       <c r="H77">
-        <v>151.36205</v>
+        <v>104.1863527</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -3776,7 +3776,7 @@
         <v>144.56662</v>
       </c>
       <c r="H78">
-        <v>243.48927</v>
+        <v>232.5774939</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -3802,7 +3802,7 @@
         <v>59.80183</v>
       </c>
       <c r="H79">
-        <v>431.97589</v>
+        <v>384.1832895</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -3828,7 +3828,7 @@
         <v>11.5067</v>
       </c>
       <c r="H80">
-        <v>209.22855</v>
+        <v>202.5927111</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3854,7 +3854,7 @@
         <v>609.70767</v>
       </c>
       <c r="H81">
-        <v>453.34248</v>
+        <v>480.4265166</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3880,7 +3880,7 @@
         <v>18.88844</v>
       </c>
       <c r="H82">
-        <v>147.99592</v>
+        <v>139.3124555</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3906,7 +3906,7 @@
         <v>481.18286</v>
       </c>
       <c r="H83">
-        <v>550.55198</v>
+        <v>574.4195714</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3932,7 +3932,7 @@
         <v>80.84356</v>
       </c>
       <c r="H84">
-        <v>370.83731</v>
+        <v>370.8373101</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3958,7 +3958,7 @@
         <v>375.7266</v>
       </c>
       <c r="H85">
-        <v>491.38756</v>
+        <v>555.4555221000001</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3984,7 +3984,7 @@
         <v>29.33239</v>
       </c>
       <c r="H86">
-        <v>107.34936</v>
+        <v>73.00430900000001</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -4010,7 +4010,7 @@
         <v>66.88285</v>
       </c>
       <c r="H87">
-        <v>253.10728</v>
+        <v>253.1072773</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -4036,7 +4036,7 @@
         <v>88.85382</v>
       </c>
       <c r="H88">
-        <v>264.62087</v>
+        <v>228.6382888</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -4062,7 +4062,7 @@
         <v>89.53541</v>
       </c>
       <c r="H89">
-        <v>234.19798</v>
+        <v>226.8581502</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -4088,7 +4088,7 @@
         <v>36.78721</v>
       </c>
       <c r="H90">
-        <v>108.37578</v>
+        <v>147.5965964</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -4114,7 +4114,7 @@
         <v>12.02195</v>
       </c>
       <c r="H91">
-        <v>95.75509</v>
+        <v>106.2006757</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -4140,7 +4140,7 @@
         <v>1124.88244</v>
       </c>
       <c r="H92">
-        <v>2227.73004</v>
+        <v>2227.730041</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -4166,7 +4166,7 @@
         <v>213.92586</v>
       </c>
       <c r="H93">
-        <v>1033.82058</v>
+        <v>1033.820576</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -4192,7 +4192,7 @@
         <v>1121.76326</v>
       </c>
       <c r="H94">
-        <v>2223.246</v>
+        <v>2223.245998</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -4218,7 +4218,7 @@
         <v>1120.19531</v>
       </c>
       <c r="H95">
-        <v>2221.58057</v>
+        <v>2221.580573</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -4244,7 +4244,7 @@
         <v>26.98927</v>
       </c>
       <c r="H96">
-        <v>249.25491</v>
+        <v>293.4965592</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -4270,7 +4270,7 @@
         <v>58.14032</v>
       </c>
       <c r="H97">
-        <v>182.42316</v>
+        <v>176.6341474</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -4296,7 +4296,7 @@
         <v>72.40939</v>
       </c>
       <c r="H98">
-        <v>209.8641</v>
+        <v>209.8640959</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -4322,7 +4322,7 @@
         <v>2.23919</v>
       </c>
       <c r="H99">
-        <v>45.8165</v>
+        <v>45.81650254</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4348,7 +4348,7 @@
         <v>2.18193</v>
       </c>
       <c r="H100">
-        <v>45.18189</v>
+        <v>45.18188837</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -4374,7 +4374,7 @@
         <v>169.26881</v>
       </c>
       <c r="H101">
-        <v>396.52041</v>
+        <v>356.9325512</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -4400,7 +4400,7 @@
         <v>75.62676</v>
       </c>
       <c r="H102">
-        <v>195.04449</v>
+        <v>166.8880513</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -4426,7 +4426,7 @@
         <v>449.74868</v>
       </c>
       <c r="H103">
-        <v>679.31738</v>
+        <v>704.1446911</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4452,7 +4452,7 @@
         <v>108.28301</v>
       </c>
       <c r="H104">
-        <v>341.42474</v>
+        <v>341.4247366</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -4478,7 +4478,7 @@
         <v>0.06672</v>
       </c>
       <c r="H105">
-        <v>79.92493</v>
+        <v>79.9249287</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -4504,7 +4504,7 @@
         <v>0.63034</v>
       </c>
       <c r="H106">
-        <v>203.71466</v>
+        <v>203.7146625</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -4530,7 +4530,7 @@
         <v>10.14636</v>
       </c>
       <c r="H107">
-        <v>64.27652</v>
+        <v>64.27652329999999</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4556,7 +4556,7 @@
         <v>69.67555</v>
       </c>
       <c r="H108">
-        <v>188.22355</v>
+        <v>190.2029111</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -4582,7 +4582,7 @@
         <v>4.22954</v>
       </c>
       <c r="H109">
-        <v>107.78693</v>
+        <v>97.33015525</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -4608,7 +4608,7 @@
         <v>4.16556</v>
       </c>
       <c r="H110">
-        <v>106.91088</v>
+        <v>95.21550159</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -4634,7 +4634,7 @@
         <v>20.14459</v>
       </c>
       <c r="H111">
-        <v>454.39211</v>
+        <v>450.4330312</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4660,7 +4660,7 @@
         <v>17.64302</v>
       </c>
       <c r="H112">
-        <v>422.64692</v>
+        <v>424.1038168</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4686,7 +4686,7 @@
         <v>59.25748</v>
       </c>
       <c r="H113">
-        <v>430.16445</v>
+        <v>378.8881622</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4712,7 +4712,7 @@
         <v>0.56514</v>
       </c>
       <c r="H114">
-        <v>60.63056</v>
+        <v>60.6305636</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -4738,7 +4738,7 @@
         <v>9.533379999999999</v>
       </c>
       <c r="H115">
-        <v>188.33894</v>
+        <v>162.6496023</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -4764,7 +4764,7 @@
         <v>211.89897</v>
       </c>
       <c r="H116">
-        <v>450.74347</v>
+        <v>450.7434656</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4790,7 +4790,7 @@
         <v>31.28307</v>
       </c>
       <c r="H117">
-        <v>109.02128</v>
+        <v>97.16028117</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4816,7 +4816,7 @@
         <v>35.6519</v>
       </c>
       <c r="H118">
-        <v>146.10114</v>
+        <v>165.3948194</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4842,7 +4842,7 @@
         <v>49.50871</v>
       </c>
       <c r="H119">
-        <v>175.41035</v>
+        <v>158.418245</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4868,7 +4868,7 @@
         <v>2.96128</v>
       </c>
       <c r="H120">
-        <v>62.88404</v>
+        <v>59.70445015</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4894,7 +4894,7 @@
         <v>436.904</v>
       </c>
       <c r="H121">
-        <v>385.31274</v>
+        <v>385.3127378</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4920,7 +4920,7 @@
         <v>155.15948</v>
       </c>
       <c r="H122">
-        <v>602.59106</v>
+        <v>602.5910599</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4946,7 +4946,7 @@
         <v>149.50304</v>
       </c>
       <c r="H123">
-        <v>624.45727</v>
+        <v>624.4572732</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4972,7 +4972,7 @@
         <v>48.8823</v>
       </c>
       <c r="H124">
-        <v>165.7883</v>
+        <v>171.1740594</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4998,7 +4998,7 @@
         <v>17.20373</v>
       </c>
       <c r="H125">
-        <v>140.2288</v>
+        <v>135.3386668</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -5024,7 +5024,7 @@
         <v>65.09520999999999</v>
       </c>
       <c r="H126">
-        <v>186.12358</v>
+        <v>186.1235839</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -5050,7 +5050,7 @@
         <v>385.72541</v>
       </c>
       <c r="H127">
-        <v>498.21076</v>
+        <v>498.2107579</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -5076,7 +5076,7 @@
         <v>126.72288</v>
       </c>
       <c r="H128">
-        <v>417.70583</v>
+        <v>407.6191257</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -5102,7 +5102,7 @@
         <v>0.70591</v>
       </c>
       <c r="H129">
-        <v>24.52641</v>
+        <v>28.61801888</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -5128,7 +5128,7 @@
         <v>562.64216</v>
       </c>
       <c r="H130">
-        <v>1458.58727</v>
+        <v>1458.587266</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -5154,7 +5154,7 @@
         <v>0.80711</v>
       </c>
       <c r="H131">
-        <v>65.81928000000001</v>
+        <v>65.81928175</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -5180,7 +5180,7 @@
         <v>1064.38633</v>
       </c>
       <c r="H132">
-        <v>2184.32078</v>
+        <v>2184.320781</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -5206,7 +5206,7 @@
         <v>150.92994</v>
       </c>
       <c r="H133">
-        <v>618.94098</v>
+        <v>618.9409849</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -5232,7 +5232,7 @@
         <v>219.71908</v>
       </c>
       <c r="H134">
-        <v>470.86116</v>
+        <v>470.8611584</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -5258,7 +5258,7 @@
         <v>118.51182</v>
       </c>
       <c r="H135">
-        <v>559.2585</v>
+        <v>559.2584986000001</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -5284,7 +5284,7 @@
         <v>95.90494</v>
       </c>
       <c r="H136">
-        <v>311.03714</v>
+        <v>311.0371356</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -5310,7 +5310,7 @@
         <v>85.54796</v>
       </c>
       <c r="H137">
-        <v>281.30776</v>
+        <v>281.3077623</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -5336,7 +5336,7 @@
         <v>44.75064</v>
       </c>
       <c r="H138">
-        <v>132.70652</v>
+        <v>132.7065202</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -5362,7 +5362,7 @@
         <v>979.4998000000001</v>
       </c>
       <c r="H139">
-        <v>2093.11085</v>
+        <v>2093.110848</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -5388,7 +5388,7 @@
         <v>58.65605</v>
       </c>
       <c r="H140">
-        <v>194.57477</v>
+        <v>194.5747711</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -5414,7 +5414,7 @@
         <v>14.5867</v>
       </c>
       <c r="H141">
-        <v>111.41126</v>
+        <v>111.4112623</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -5440,7 +5440,7 @@
         <v>16.92368</v>
       </c>
       <c r="H142">
-        <v>100.84354</v>
+        <v>100.8435387</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -5466,7 +5466,7 @@
         <v>301.9744</v>
       </c>
       <c r="H143">
-        <v>581.56073</v>
+        <v>574.973943</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -5492,7 +5492,7 @@
         <v>114.70867</v>
       </c>
       <c r="H144">
-        <v>554.27678</v>
+        <v>554.2767798</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -5518,7 +5518,7 @@
         <v>350.50216</v>
       </c>
       <c r="H145">
-        <v>352.17459</v>
+        <v>352.1745913</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5544,7 +5544,7 @@
         <v>0.41975</v>
       </c>
       <c r="H146">
-        <v>38.98056</v>
+        <v>59.18334812</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5570,7 +5570,7 @@
         <v>79.1035</v>
       </c>
       <c r="H147">
-        <v>215.82104</v>
+        <v>199.0433777</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5596,7 +5596,7 @@
         <v>1.68593</v>
       </c>
       <c r="H148">
-        <v>75.63366000000001</v>
+        <v>75.63366447999999</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5622,7 +5622,7 @@
         <v>96.41773000000001</v>
       </c>
       <c r="H149">
-        <v>188.65051</v>
+        <v>140.8408204</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5648,7 +5648,7 @@
         <v>19.6369</v>
       </c>
       <c r="H150">
-        <v>208.54603</v>
+        <v>225.0851048</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5674,7 +5674,7 @@
         <v>300.64</v>
       </c>
       <c r="H151">
-        <v>546.06037</v>
+        <v>546.0603692</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5700,7 +5700,7 @@
         <v>134.77547</v>
       </c>
       <c r="H152">
-        <v>348.09711</v>
+        <v>327.7207185</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5726,7 +5726,7 @@
         <v>31.24472</v>
       </c>
       <c r="H153">
-        <v>143.30426</v>
+        <v>143.3042563</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5752,7 +5752,7 @@
         <v>521.4169000000001</v>
       </c>
       <c r="H154">
-        <v>417.82808</v>
+        <v>427.7993497</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5778,7 +5778,7 @@
         <v>30.69896</v>
       </c>
       <c r="H155">
-        <v>107.98782</v>
+        <v>107.9878199</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5804,7 +5804,7 @@
         <v>132.61118</v>
       </c>
       <c r="H156">
-        <v>277.45713</v>
+        <v>277.4571276</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5830,7 +5830,7 @@
         <v>233.74278</v>
       </c>
       <c r="H157">
-        <v>478.7421</v>
+        <v>478.7421014</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5856,7 +5856,7 @@
         <v>139.25024</v>
       </c>
       <c r="H158">
-        <v>208.74063</v>
+        <v>217.0628986</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5882,7 +5882,7 @@
         <v>376.00064</v>
       </c>
       <c r="H159">
-        <v>482.59281</v>
+        <v>482.5928085</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5908,7 +5908,7 @@
         <v>33.43533</v>
       </c>
       <c r="H160">
-        <v>117.15417</v>
+        <v>117.1541699</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5934,7 +5934,7 @@
         <v>37.72776</v>
       </c>
       <c r="H161">
-        <v>148.81781</v>
+        <v>148.817814</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5960,7 +5960,7 @@
         <v>64.57172</v>
       </c>
       <c r="H162">
-        <v>182.24747</v>
+        <v>182.2474679</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5986,7 +5986,7 @@
         <v>66.46401</v>
       </c>
       <c r="H163">
-        <v>181.43883</v>
+        <v>195.1452498</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -6012,7 +6012,7 @@
         <v>71.87951</v>
       </c>
       <c r="H164">
-        <v>260.40822</v>
+        <v>260.4082207</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -6038,7 +6038,7 @@
         <v>0.13066</v>
       </c>
       <c r="H165">
-        <v>111.11633</v>
+        <v>111.1163328</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -6064,7 +6064,7 @@
         <v>118.79584</v>
       </c>
       <c r="H166">
-        <v>218.97891</v>
+        <v>127.781814</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -6090,7 +6090,7 @@
         <v>8.413500000000001</v>
       </c>
       <c r="H167">
-        <v>58.79938</v>
+        <v>51.55383838</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -6116,7 +6116,7 @@
         <v>3.32215</v>
       </c>
       <c r="H168">
-        <v>94.54282000000001</v>
+        <v>91.09965602</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -6142,7 +6142,7 @@
         <v>0.55186</v>
       </c>
       <c r="H169">
-        <v>25.88878</v>
+        <v>41.37177431</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -6168,7 +6168,7 @@
         <v>34.83736</v>
       </c>
       <c r="H170">
-        <v>149.76273</v>
+        <v>149.7627284</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -6194,7 +6194,7 @@
         <v>9.98568</v>
       </c>
       <c r="H171">
-        <v>310.91233</v>
+        <v>381.0056244</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -6220,7 +6220,7 @@
         <v>317.24685</v>
       </c>
       <c r="H172">
-        <v>569.95144</v>
+        <v>540.8951886999999</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -6246,7 +6246,7 @@
         <v>0.36686</v>
       </c>
       <c r="H173">
-        <v>53.13674</v>
+        <v>53.13673781</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -6272,7 +6272,7 @@
         <v>7.63123</v>
       </c>
       <c r="H174">
-        <v>166.88239</v>
+        <v>166.8823866</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -6298,7 +6298,7 @@
         <v>47.35314</v>
       </c>
       <c r="H175">
-        <v>168.40935</v>
+        <v>168.4093544</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -6324,7 +6324,7 @@
         <v>613.52968</v>
       </c>
       <c r="H176">
-        <v>455.82605</v>
+        <v>455.8260489</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6350,7 +6350,7 @@
         <v>0.07474</v>
       </c>
       <c r="H177">
-        <v>17.45356</v>
+        <v>17.45356054</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6376,7 +6376,7 @@
         <v>127.83915</v>
       </c>
       <c r="H178">
-        <v>205.31155</v>
+        <v>163.4238441</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6428,7 +6428,7 @@
         <v>45.38484</v>
       </c>
       <c r="H180">
-        <v>120.42323</v>
+        <v>120.4232252</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6454,7 +6454,7 @@
         <v>2.43629</v>
       </c>
       <c r="H181">
-        <v>56.58128</v>
+        <v>55.73721066</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6480,7 +6480,7 @@
         <v>497.00602</v>
       </c>
       <c r="H182">
-        <v>414.25507</v>
+        <v>414.2550708</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -6506,7 +6506,7 @@
         <v>489.45791</v>
       </c>
       <c r="H183">
-        <v>557.29258</v>
+        <v>557.2925755</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6532,7 +6532,7 @@
         <v>58.58758</v>
       </c>
       <c r="H184">
-        <v>311.19341</v>
+        <v>311.1934079</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -6558,7 +6558,7 @@
         <v>56.58464</v>
       </c>
       <c r="H185">
-        <v>179.51759</v>
+        <v>198.7036887</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -6584,7 +6584,7 @@
         <v>41.25684</v>
       </c>
       <c r="H186">
-        <v>162.30259</v>
+        <v>162.302586</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -6610,7 +6610,7 @@
         <v>13.93874</v>
       </c>
       <c r="H187">
-        <v>124.72797</v>
+        <v>158.3086448</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -6636,7 +6636,7 @@
         <v>63.31627</v>
       </c>
       <c r="H188">
-        <v>183.0433</v>
+        <v>201.115576</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -6662,7 +6662,7 @@
         <v>363.71771</v>
       </c>
       <c r="H189">
-        <v>482.71094</v>
+        <v>482.7109415</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6688,7 +6688,7 @@
         <v>99.92854</v>
       </c>
       <c r="H190">
-        <v>367.73594</v>
+        <v>315.7042727</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6714,7 +6714,7 @@
         <v>58.232</v>
       </c>
       <c r="H191">
-        <v>234.12846</v>
+        <v>249.0778521</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6740,7 +6740,7 @@
         <v>21.01632</v>
       </c>
       <c r="H192">
-        <v>104.32381</v>
+        <v>104.323809</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6766,7 +6766,7 @@
         <v>80.62768</v>
       </c>
       <c r="H193">
-        <v>251.15681</v>
+        <v>251.1568141</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6792,7 +6792,7 @@
         <v>107.35674</v>
       </c>
       <c r="H194">
-        <v>340.67497</v>
+        <v>340.6749733</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6818,7 +6818,7 @@
         <v>55.59432</v>
       </c>
       <c r="H195">
-        <v>203.05694</v>
+        <v>109.5355043</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6844,7 +6844,7 @@
         <v>151.74135</v>
       </c>
       <c r="H196">
-        <v>629.96801</v>
+        <v>629.9680144</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6870,7 +6870,7 @@
         <v>1115.81485</v>
       </c>
       <c r="H197">
-        <v>2215.31524</v>
+        <v>2215.315238</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6896,7 +6896,7 @@
         <v>92.77632</v>
       </c>
       <c r="H198">
-        <v>499.44345</v>
+        <v>499.4434511</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6922,7 +6922,7 @@
         <v>0.35737</v>
       </c>
       <c r="H199">
-        <v>74.44182000000001</v>
+        <v>74.4418173</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6948,7 +6948,7 @@
         <v>14.03149</v>
       </c>
       <c r="H200">
-        <v>103.95113</v>
+        <v>103.9511289</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6974,7 +6974,7 @@
         <v>208.07071</v>
       </c>
       <c r="H201">
-        <v>477.31251</v>
+        <v>477.3125143</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -7000,7 +7000,7 @@
         <v>182.82548</v>
       </c>
       <c r="H202">
-        <v>428.98346</v>
+        <v>428.9834607</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -7026,7 +7026,7 @@
         <v>305.72938</v>
       </c>
       <c r="H203">
-        <v>452.4393</v>
+        <v>452.4393037</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -7052,7 +7052,7 @@
         <v>73.83902</v>
       </c>
       <c r="H204">
-        <v>224.91541</v>
+        <v>224.9154138</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -7078,7 +7078,7 @@
         <v>113.68134</v>
       </c>
       <c r="H205">
-        <v>360.54536</v>
+        <v>324.3005331</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -7104,7 +7104,7 @@
         <v>382.02475</v>
       </c>
       <c r="H206">
-        <v>368.08453</v>
+        <v>393.984242</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -7130,7 +7130,7 @@
         <v>257.68165</v>
       </c>
       <c r="H207">
-        <v>1258.52059</v>
+        <v>1258.520595</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -7156,7 +7156,7 @@
         <v>45.23424</v>
       </c>
       <c r="H208">
-        <v>130.46977</v>
+        <v>130.4697659</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -7182,7 +7182,7 @@
         <v>533.36799</v>
       </c>
       <c r="H209">
-        <v>1518.92523</v>
+        <v>1518.925229</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -7208,7 +7208,7 @@
         <v>1.64409</v>
       </c>
       <c r="H210">
-        <v>38.749</v>
+        <v>38.74899962</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7234,7 +7234,7 @@
         <v>54.028</v>
       </c>
       <c r="H211">
-        <v>223.09604</v>
+        <v>223.0960354</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -7260,7 +7260,7 @@
         <v>8.30302</v>
       </c>
       <c r="H212">
-        <v>55.34707</v>
+        <v>55.34707289</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -7286,7 +7286,7 @@
         <v>10.30624</v>
       </c>
       <c r="H213">
-        <v>316.30488</v>
+        <v>316.3048755</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -7312,7 +7312,7 @@
         <v>26.25005</v>
       </c>
       <c r="H214">
-        <v>274.97388</v>
+        <v>274.9738817</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -7338,7 +7338,7 @@
         <v>2.24024</v>
       </c>
       <c r="H215">
-        <v>54.08546</v>
+        <v>54.08545774</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -7364,7 +7364,7 @@
         <v>30.81269</v>
       </c>
       <c r="H216">
-        <v>220.95829</v>
+        <v>220.9582893</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -7390,7 +7390,7 @@
         <v>30.73846</v>
       </c>
       <c r="H217">
-        <v>138.65404</v>
+        <v>138.6540404</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -7416,7 +7416,7 @@
         <v>18.16668</v>
       </c>
       <c r="H218">
-        <v>143.11772</v>
+        <v>118.2919895</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7442,7 +7442,7 @@
         <v>175.041</v>
       </c>
       <c r="H219">
-        <v>252.4995</v>
+        <v>252.4995018</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -7468,7 +7468,7 @@
         <v>24.87416</v>
       </c>
       <c r="H220">
-        <v>113.978</v>
+        <v>113.9780024</v>
       </c>
     </row>
     <row r="221" spans="1:8">
